--- a/artfynd/A 34105-2019 artfynd.xlsx
+++ b/artfynd/A 34105-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34105-2019 artfynd.xlsx
+++ b/artfynd/A 34105-2019 artfynd.xlsx
@@ -4985,7 +4985,7 @@
         <v>80572221</v>
       </c>
       <c r="B40" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>556481.1408774862</v>
+        <v>556481</v>
       </c>
       <c r="R40" t="n">
-        <v>6946577.197186184</v>
+        <v>6946577</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5055,19 +5055,9 @@
           <t>2019-10-19</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2019-10-19</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -7123,7 +7113,7 @@
         <v>81134062</v>
       </c>
       <c r="B59" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7165,10 +7155,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556744.9935589804</v>
+        <v>556745</v>
       </c>
       <c r="R59" t="n">
-        <v>6946340.227095835</v>
+        <v>6946340</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7198,19 +7188,9 @@
           <t>2019-08-25</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2019-10-25</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8472,7 +8452,7 @@
         <v>81134100</v>
       </c>
       <c r="B71" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8514,10 +8494,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556799.202809872</v>
+        <v>556799</v>
       </c>
       <c r="R71" t="n">
-        <v>6946295.158105395</v>
+        <v>6946295</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8547,19 +8527,9 @@
           <t>2019-08-25</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2019-10-25</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9955,7 +9925,7 @@
         <v>87862779</v>
       </c>
       <c r="B84" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10000,10 +9970,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>556650.0786505375</v>
+        <v>556650</v>
       </c>
       <c r="R84" t="n">
-        <v>6946502.813128014</v>
+        <v>6946503</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10033,19 +10003,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -13200,7 +13160,7 @@
         <v>96072435</v>
       </c>
       <c r="B112" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13241,10 +13201,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>556496.3759663707</v>
+        <v>556497</v>
       </c>
       <c r="R112" t="n">
-        <v>6946575.1576629</v>
+        <v>6946575</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13274,19 +13234,9 @@
           <t>2021-09-12</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -13553,7 +13503,7 @@
         <v>96071371</v>
       </c>
       <c r="B115" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13594,10 +13544,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>556263.4324829889</v>
+        <v>556264</v>
       </c>
       <c r="R115" t="n">
-        <v>6946648.91787409</v>
+        <v>6946649</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13627,19 +13577,9 @@
           <t>2021-09-12</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -13674,7 +13614,7 @@
         <v>96081520</v>
       </c>
       <c r="B116" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13715,10 +13655,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>556798.8133774067</v>
+        <v>556799</v>
       </c>
       <c r="R116" t="n">
-        <v>6946291.011417183</v>
+        <v>6946291</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13748,19 +13688,9 @@
           <t>2021-09-12</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -14027,7 +13957,7 @@
         <v>96081557</v>
       </c>
       <c r="B119" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14068,10 +13998,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>556809.850034215</v>
+        <v>556810</v>
       </c>
       <c r="R119" t="n">
-        <v>6946292.120997153</v>
+        <v>6946292</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -14101,19 +14031,9 @@
           <t>2021-09-12</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -16829,7 +16749,7 @@
         <v>96072669</v>
       </c>
       <c r="B143" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16870,10 +16790,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>556508.6375510056</v>
+        <v>556509</v>
       </c>
       <c r="R143" t="n">
-        <v>6946639.300906397</v>
+        <v>6946639</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -16903,19 +16823,9 @@
           <t>2021-09-12</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
@@ -17298,7 +17208,7 @@
         <v>96072282</v>
       </c>
       <c r="B147" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17343,10 +17253,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>556482.6980593303</v>
+        <v>556483</v>
       </c>
       <c r="R147" t="n">
-        <v>6946539.966909532</v>
+        <v>6946540</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -17376,19 +17286,9 @@
           <t>2021-09-12</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -19508,7 +19408,7 @@
         <v>102450708</v>
       </c>
       <c r="B166" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19549,10 +19449,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>556496.4466755582</v>
+        <v>556496</v>
       </c>
       <c r="R166" t="n">
-        <v>6946571.019235576</v>
+        <v>6946571</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -19582,19 +19482,9 @@
           <t>2022-07-24</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2022-07-24</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC166" t="inlineStr">

--- a/artfynd/A 34105-2019 artfynd.xlsx
+++ b/artfynd/A 34105-2019 artfynd.xlsx
@@ -4985,7 +4985,7 @@
         <v>80572221</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>81134062</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>81134100</v>
       </c>
       <c r="B71" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>87862779</v>
       </c>
       <c r="B84" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>96072435</v>
       </c>
       <c r="B112" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>96071371</v>
       </c>
       <c r="B115" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>96081520</v>
       </c>
       <c r="B116" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>96081557</v>
       </c>
       <c r="B119" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>96072669</v>
       </c>
       <c r="B143" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>96072282</v>
       </c>
       <c r="B147" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>102450708</v>
       </c>
       <c r="B166" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>

--- a/artfynd/A 34105-2019 artfynd.xlsx
+++ b/artfynd/A 34105-2019 artfynd.xlsx
@@ -4985,7 +4985,7 @@
         <v>80572221</v>
       </c>
       <c r="B40" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>81134062</v>
       </c>
       <c r="B59" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>81134100</v>
       </c>
       <c r="B71" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>87862779</v>
       </c>
       <c r="B84" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>96072435</v>
       </c>
       <c r="B112" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>96071371</v>
       </c>
       <c r="B115" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>96081520</v>
       </c>
       <c r="B116" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>96081557</v>
       </c>
       <c r="B119" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>96072669</v>
       </c>
       <c r="B143" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>96072282</v>
       </c>
       <c r="B147" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>102450708</v>
       </c>
       <c r="B166" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
